--- a/var/data/original_files/Articles A July 21.xlsx
+++ b/var/data/original_files/Articles A July 21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,11 +488,6 @@
           <t>Full Link</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Coordinates</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -531,7 +526,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Human, Infrastructure</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -542,38 +537,33 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>https://www.reuters.com/world/several-injured-rome-after-gas-station-explodes-reports-2025-07-04/</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>(41.8933203, 12.4829321)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Huge explosion at Rome petrol station injures 45 people</t>
+          <t>United Kingdom contributes £400,000 to support OPCW’s ongoing work in Ukraine</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -583,57 +573,52 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/several-injured-rome-after-gas-station-explodes-reports-2025-07-04/</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>(41.8933203, 12.4829321)</t>
+          <t>https://www.opcw.org/media-centre/news/2025/07/united-kingdom-contributes-ps400000-support-opcws-ongoing-work-ukraine</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>United Kingdom contributes £400,000 to support OPCW’s ongoing work in Ukraine</t>
+          <t>Monkeypox Virus Disarms the Body’s Immune Alarm: New Study Uncovers Viral Sabotage Tactic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Wuhan</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45842</v>
+        <v>45844</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -643,7 +628,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -653,39 +638,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.opcw.org/media-centre/news/2025/07/united-kingdom-contributes-ps400000-support-opcws-ongoing-work-ukraine</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>(51.5029954, -0.0014602)</t>
+          <t>https://globalbiodefense.com/2025/07/06/mpox-monkeypox-virus-immune-evasion-opg147/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Monkeypox Virus Disarms the Body’s Immune Alarm: New Study Uncovers Viral Sabotage Tactic</t>
+          <t>Explosion damages tanker in Russian port, marking 6th mysterious blast this year</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuhan</t>
+          <t>Ust-Luga</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -699,7 +679,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Environment, Infrastructure</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,43 +689,38 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/07/06/mpox-monkeypox-virus-immune-evasion-opg147/</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>(30.5951051, 114.2999353)</t>
+          <t>https://kyivindependent.com/explosion-on-tanker-in-russian-port-sparks-investigation-06-2025/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear, Radiological</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Explosion damages tanker in Russian port, marking 6th mysterious blast this year</t>
+          <t>Call for Papers: Conference on Transport of Nuclear and Radioactive Material</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ust-Luga</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45844</v>
+        <v>45845</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -765,43 +740,38 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://kyivindependent.com/explosion-on-tanker-in-russian-port-sparks-investigation-06-2025/</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>(59.659244, 28.2695087)</t>
+          <t>https://www.iaea.org/newscenter/news/call-for-papers-conference-on-transport-of-nuclear-and-radioactive-material</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Explosion damages tanker in Russian port, marking 6th mysterious blast this year</t>
+          <t>Design Considerations for Nuclear Power Plants Against Tsunamis</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ust-Luga</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45844</v>
+        <v>45845</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -821,19 +791,14 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://kyivindependent.com/explosion-on-tanker-in-russian-port-sparks-investigation-06-2025/</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>(59.659244, 28.2695087)</t>
+          <t>https://www.iaea.org/publications/15768/design-considerations-for-nuclear-power-plants-against-tsunamis</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -843,7 +808,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Call for Papers: Conference on Transport of Nuclear and Radioactive Material</t>
+          <t>UN nuclear chief says military force cannot end Iran nuclear standoff</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -867,7 +832,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -877,43 +842,38 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/call-for-papers-conference-on-transport-of-nuclear-and-radioactive-material</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
+          <t>https://www.iranintl.com/en/202507074367</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear, Radiological</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Call for Papers: Conference on Transport of Nuclear and Radioactive Material</t>
+          <t>Tepco plans to move spent nuclear fuel from Fukushima to Mutsu facility</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t xml:space="preserve">Mutsu </t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -923,7 +883,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -933,19 +893,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/call-for-papers-conference-on-transport-of-nuclear-and-radioactive-material</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
+          <t>https://www.japantimes.co.jp/news/2025/07/08/japan/tepco-move-mutsu/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -955,17 +910,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Design Considerations for Nuclear Power Plants Against Tsunamis</t>
+          <t>Russia Seeks Leverage in Iran Nuclear Talks by Offering Uranium Deal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -989,12 +944,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/publications/15768/design-considerations-for-nuclear-power-plants-against-tsunamis</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
+          <t>https://united24media.com/latest-news/russia-seeks-leverage-in-iran-nuclear-talks-by-offering-uranium-deal-9687</t>
         </is>
       </c>
     </row>
@@ -1011,21 +961,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UN nuclear chief says military force cannot end Iran nuclear standoff</t>
+          <t>King Abdulaziz University Students Join International Program to Boost National Nuclear Energy Capabilities</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1045,12 +995,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.iranintl.com/en/202507074367</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
+          <t>https://www.spa.gov.sa/en/N2353280</t>
         </is>
       </c>
     </row>
@@ -1067,21 +1012,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tepco plans to move spent nuclear fuel from Fukushima to Mutsu facility</t>
+          <t>Sweden Funds IAEA Nuclear Safety Missions in Ukraine with 20 Million SEK in 2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mutsu </t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45846</v>
+        <v>45845</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1091,7 +1036,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1101,43 +1046,38 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.japantimes.co.jp/news/2025/07/08/japan/tepco-move-mutsu/</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>(41.2928444, 141.1831247)</t>
+          <t>https://mezha.net/eng/bukvy/sweden-funds-iaea-nuclear-safety-missions-in-ukraine-with-20-million-sek-in-2025/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Exercise</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tepco plans to move spent nuclear fuel from Fukushima to Mutsu facility</t>
+          <t>FEMA to conduct training exercise at Surry nuclear power plant</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mutsu </t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45846</v>
+        <v>45845</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1147,7 +1087,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Human, Infrastructure</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1157,12 +1097,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.japantimes.co.jp/news/2025/07/08/japan/tepco-move-mutsu/</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>(41.2928444, 141.1831247)</t>
+          <t>https://www.13newsnow.com/article/news/local/virginia/fema-emergency-preparedness-exercise-surry-power-station-nuclear-power-plant/291-36b9b5fd-9077-4f47-9fc2-eef688aa452b</t>
         </is>
       </c>
     </row>
@@ -1174,22 +1109,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Nuclear, Radiological</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Seeks Leverage in Iran Nuclear Talks by Offering Uranium Deal</t>
+          <t>Saudi Arabia is working to enhance its counter-contamination and radiological preparedness framework</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1203,7 +1138,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human, Environment</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1213,43 +1148,38 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://united24media.com/latest-news/russia-seeks-leverage-in-iran-nuclear-talks-by-offering-uranium-deal-9687</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>(55.625578, 37.6063916)</t>
+          <t>https://www.tacticalreport.com/daily/63659-saudi-cbrn-preparedness-eyed-equipment-and-countries-for-cooperation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>King Abdulaziz University Students Join International Program to Boost National Nuclear Energy Capabilities</t>
+          <t>Tanker explosion off Gujarat coast forces crew to abandon ship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45846</v>
+        <v>45845</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1259,7 +1189,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1269,43 +1199,38 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.spa.gov.sa/en/N2353280</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>(21.5504432, 39.1742363)</t>
+          <t>https://safety4sea.com/tanker-explosion-off-gujarat-coast-forces-crew-to-abandon-ship/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Funds IAEA Nuclear Safety Missions in Ukraine with 20 Million SEK in 2025</t>
+          <t>Scientists discover how H5N1 virus invades cattle</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t xml:space="preserve">Heilongjiang </t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1315,7 +1240,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1325,49 +1250,40 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://mezha.net/eng/bukvy/sweden-funds-iaea-nuclear-safety-missions-in-ukraine-with-20-million-sek-in-2025/</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>(59.3251172, 18.0710935)</t>
+          <t>https://www.chinadaily.com.cn/a/202507/08/WS686c7517a31000e9a573ab45.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Exercise</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FEMA to conduct training exercise at Surry nuclear power plant</t>
+          <t>Epidemic and emerging disease alerts in the Pacific as of 8 July 2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Virginia</t>
-        </is>
-      </c>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1381,43 +1297,38 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.13newsnow.com/article/news/local/virginia/fema-emergency-preparedness-exercise-surry-power-station-nuclear-power-plant/291-36b9b5fd-9077-4f47-9fc2-eef688aa452b</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>(36.8496579, -75.9760751)</t>
+          <t>https://reliefweb.int/map/world/epidemic-and-emerging-disease-alerts-pacific-8-july-2025</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Exercise</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FEMA to conduct training exercise at Surry nuclear power plant</t>
+          <t>UK sanctions Russian generals and military lab for chemical warfare in Ukraine</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1427,7 +1338,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1437,43 +1348,38 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.13newsnow.com/article/news/local/virginia/fema-emergency-preparedness-exercise-surry-power-station-nuclear-power-plant/291-36b9b5fd-9077-4f47-9fc2-eef688aa452b</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>(36.8496579, -75.9760751)</t>
+          <t>https://euromaidanpress.com/2025/07/08/uk-sanctions-russian-generals-and-military-lab-for-chemical-warfare-in-ukraine/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia is working to enhance its counter-contamination and radiological preparedness framework</t>
+          <t>Assessing the Utility of the COVID-19 Epidemic Situations of Concern (SOC) Classification System in Guiding Operational Responses to the Pandemic in the WHO African Region: Retrospective analysis</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Kinshasa</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1483,7 +1389,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1493,12 +1399,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.tacticalreport.com/daily/63659-saudi-cbrn-preparedness-eyed-equipment-and-countries-for-cooperation</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>(23.333333, 45.333333)</t>
+          <t>https://www.frontiersin.org/journals/public-health/articles/10.3389/fpubh.2025.1562525/abstract</t>
         </is>
       </c>
     </row>
@@ -1510,22 +1411,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia is working to enhance its counter-contamination and radiological preparedness framework</t>
+          <t>Swiss-Japanese Experiences of Epidemics and Pandemics</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Osaka</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1539,7 +1440,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1549,43 +1450,38 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.tacticalreport.com/daily/63659-saudi-cbrn-preparedness-eyed-equipment-and-countries-for-cooperation</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>(23.333333, 45.333333)</t>
+          <t>https://www.unil.ch/news/en/1751879732708</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia is working to enhance its counter-contamination and radiological preparedness framework</t>
+          <t>Annual Review Meeting of the implementation of Pandemic Influenza Preparedness (PIP) Partnership Contribution (PC) Funding the South-East Asia Region and the simulation exercise on Preparedness and Resilience for Emerging Threats (PRET)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Geneve</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1605,12 +1501,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.tacticalreport.com/daily/63659-saudi-cbrn-preparedness-eyed-equipment-and-countries-for-cooperation</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>(23.333333, 45.333333)</t>
+          <t>https://www.who.int/publications/i/item/SEA-WHE-25</t>
         </is>
       </c>
     </row>
@@ -1622,26 +1513,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia is working to enhance its counter-contamination and radiological preparedness framework</t>
+          <t>Swinburne University Develops Database Consolidating COVID-19 Impacts for Future Pandemic Preparedness</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Melbourne</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1651,7 +1542,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Human, Technology</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1661,43 +1552,38 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.tacticalreport.com/daily/63659-saudi-cbrn-preparedness-eyed-equipment-and-countries-for-cooperation</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>(23.333333, 45.333333)</t>
+          <t>https://www.geneonline.com/swinburne-university-develops-database-consolidating-covid-19-impacts-for-future-pandemic-preparedness/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tanker explosion off Gujarat coast forces crew to abandon ship</t>
+          <t>Seoul rules out radioactive contamination amid North Korea wastewater fears</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1707,7 +1593,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1717,43 +1603,38 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://safety4sea.com/tanker-explosion-off-gujarat-coast-forces-crew-to-abandon-ship/</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>(22.3367527, 73.2270971)</t>
+          <t>https://www.nknews.org/2025/07/seoul-rules-out-radioactive-contamination-amid-north-korea-wastewater-fears/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scientists discover how H5N1 virus invades cattle</t>
+          <t>15 Radioactive Smuggling Cases Detected Annually - Atom Malaysia</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heilongjiang </t>
+          <t>Johor</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45846</v>
+        <v>45845</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1763,7 +1644,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1773,39 +1654,34 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.chinadaily.com.cn/a/202507/08/WS686c7517a31000e9a573ab45.html</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>(48.0000047, 127.999992)</t>
+          <t>https://bernama.com/en/news.php?id=2442215</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UK sanctions Russian generals and military lab for chemical warfare in Ukraine</t>
+          <t>Call for Papers: International Conference on Topical Issues in Nuclear Installation Safety</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -1819,7 +1695,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1829,39 +1705,34 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://euromaidanpress.com/2025/07/08/uk-sanctions-russian-generals-and-military-lab-for-chemical-warfare-in-ukraine/</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>(51.5029954, -0.0014602)</t>
+          <t>https://www.iaea.org/newscenter/news/call-for-papers-international-conference-on-topical-issues-in-nuclear-installation-safety</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Assessing the Utility of the COVID-19 Epidemic Situations of Concern (SOC) Classification System in Guiding Operational Responses to the Pandemic in the WHO African Region: Retrospective analysis</t>
+          <t>Benchmarking Current Practices in Probabilistic Fault Displacement Hazard Analysis for Nuclear Installations</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kinshasa</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -1875,7 +1746,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1885,43 +1756,38 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.frontiersin.org/journals/public-health/articles/10.3389/fpubh.2025.1562525/abstract</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>(-4.32171, 15.3122511)</t>
+          <t>https://www.iaea.org/publications/15863/benchmarking-current-practices-in-probabilistic-fault-displacement-hazard-analysis-for-nuclear-installations</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Swiss-Japanese Experiences of Epidemics and Pandemics</t>
+          <t>Assessment of Radioactive Contamination, Exposures and Countermeasures in Urban Environments</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Osaka</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1931,7 +1797,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1941,12 +1807,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.unil.ch/news/en/1751879732708</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>(34.8965929, 134.8255815)</t>
+          <t>https://www.iaea.org/publications/15750/assessment-of-radioactive-contamination-exposures-and-countermeasures-in-urban-environments</t>
         </is>
       </c>
     </row>
@@ -1958,22 +1819,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Annual Review Meeting of the implementation of Pandemic Influenza Preparedness (PIP) Partnership Contribution (PC) Funding the South-East Asia Region and the simulation exercise on Preparedness and Resilience for Emerging Threats (PRET)</t>
+          <t>Tritium in the Environment</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Geneve</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -1987,7 +1848,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1997,19 +1858,14 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.who.int/publications/i/item/SEA-WHE-25</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
+          <t>https://www.iaea.org/publications/15287/tritium-in-the-environment</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2019,17 +1875,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Swinburne University Develops Database Consolidating COVID-19 Impacts for Future Pandemic Preparedness</t>
+          <t>New Multi-Epitope Mpox Vaccine Shows Strong Potential in Silico</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Melbourne</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2053,19 +1909,14 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.geneonline.com/swinburne-university-develops-database-consolidating-covid-19-impacts-for-future-pandemic-preparedness/</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>(-37.808747, 144.9238207)</t>
+          <t>https://globalbiodefense.com/2025/07/08/new-multi-epitope-mpox-vaccine-shows-strong-potential-in-silico/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2075,31 +1926,31 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Swinburne University Develops Database Consolidating COVID-19 Impacts for Future Pandemic Preparedness</t>
+          <t>Cambodia Reports Surge in Human Infections with Avian Influenza A(H5N1)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Melbourne</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2109,39 +1960,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.geneonline.com/swinburne-university-develops-database-consolidating-covid-19-impacts-for-future-pandemic-preparedness/</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>(-37.808747, 144.9238207)</t>
+          <t>https://globalbiodefense.com/2025/07/08/cambodia-reports-surge-in-human-infections-with-avian-influenza-ah5n1/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seoul rules out radioactive contamination amid North Korea wastewater fears</t>
+          <t>Monoclonal Antibody Shows Broad SARS-CoV-2 Neutralization in Preclinical  Study</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2155,7 +2001,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2165,12 +2011,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.nknews.org/2025/07/seoul-rules-out-radioactive-contamination-amid-north-korea-wastewater-fears/</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>(37.5666791, 126.9782914)</t>
+          <t>https://globalbiodefense.com/2025/07/08/monoclonal-antibody-shows-broad-sars-cov-2-neutralization-in-preclinical-study/</t>
         </is>
       </c>
     </row>
@@ -2182,26 +2023,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15 Radioactive Smuggling Cases Detected Annually - Atom Malaysia</t>
+          <t>Hitachi Announces ‘Metaverse’ Platform That Can Improve Nuclear Plant Construction And Maintenance</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Johor</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45845</v>
+        <v>45848</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2211,7 +2052,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2221,43 +2062,38 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://bernama.com/en/news.php?id=2442215</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>(2.0228821, 103.3114564)</t>
+          <t>https://www.nucnet.org/news/hitachi-announces-metaverse-platform-that-can-improve-nuclear-plant-construction-and-maintenance-7-4-2025</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Radiological, Chemical</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Call for Papers: International Conference on Topical Issues in Nuclear Installation Safety</t>
+          <t>مصادر دفاعية وأمنية تكشف عن تلقي الحوثيين شحنات مواد مشعة وكيماوية تستخدم لتقنية الصواريخ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Sa'dah</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2267,63 +2103,58 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/call-for-papers-international-conference-on-topical-issues-in-nuclear-installation-safety</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
+          <t>https://www.defenseliney.net/posts/295</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Benchmarking Current Practices in Probabilistic Fault Displacement Hazard Analysis for Nuclear Installations</t>
+          <t>Gas explosion at residential tower in Tehran injures four: Iranian state media</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45846</v>
+        <v>45848</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Infrastructure, Human</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2333,19 +2164,14 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/publications/15863/benchmarking-current-practices-in-probabilistic-fault-displacement-hazard-analysis-for-nuclear-installations</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
+          <t>https://english.alarabiya.net/News/middle-east/2025/07/10/gas-explosion-at-residential-tower-in-tehran-injures-four-iranian-state-media</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2355,21 +2181,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Assessment of Radioactive Contamination, Exposures and Countermeasures in Urban Environments</t>
+          <t>Russia slams report it backed ‘zero enrichment’ Iran nuclear deal</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45846</v>
+        <v>45851</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2389,12 +2215,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/publications/15750/assessment-of-radioactive-contamination-exposures-and-countermeasures-in-urban-environments</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
+          <t>https://english.alarabiya.net/News/world/2025/07/13/russia-slams-report-it-backed-zero-enrichment-iran-nuclear-deal-</t>
         </is>
       </c>
     </row>
@@ -2411,21 +2232,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tritium in the Environment</t>
+          <t>Update 302 – IAEA Director General Statement on Situation in Ukraine</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Zaporizhzhya</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45846</v>
+        <v>45850</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2445,43 +2266,38 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/publications/15287/tritium-in-the-environment</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/update-302-iaea-director-general-statement-on-situation-in-ukraine</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New Multi-Epitope Mpox Vaccine Shows Strong Potential in Silico</t>
+          <t>Update 303 – IAEA Director General Statement on Situation in Ukraine</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Zaporizhzhya</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45846</v>
+        <v>45851</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2491,7 +2307,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2501,49 +2317,48 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/07/08/new-multi-epitope-mpox-vaccine-shows-strong-potential-in-silico/</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>https://www.iaea.org/newscenter/pressreleases/update-303-iaea-director-general-statement-on-situation-in-ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cambodia Reports Surge in Human Infections with Avian Influenza A(H5N1)</t>
+          <t>Iran may resume US nuclear talks under no new attacks guarantee</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45846</v>
+        <v>45850</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2553,43 +2368,38 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/07/08/cambodia-reports-surge-in-human-infections-with-avian-influenza-ah5n1/</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>(11.5730391, 104.857807)</t>
+          <t>https://www.dailysabah.com/world/mid-east/iran-may-resume-us-nuclear-talks-under-no-new-attacks-guarantee</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monoclonal Antibody Shows Broad SARS-CoV-2 Neutralization in Preclinical  Study</t>
+          <t>Iran says it will work with IAEA but inspections may be risky</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45846</v>
+        <v>45850</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2599,7 +2409,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2609,12 +2419,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/07/08/monoclonal-antibody-shows-broad-sars-cov-2-neutralization-in-preclinical-study/</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>(40.7856117, -74.0093129)</t>
+          <t>https://www.reuters.com/world/middle-east/fm-araqchi-says-iran-work-with-iaea-inspections-may-be-risky-2025-07-12/</t>
         </is>
       </c>
     </row>
@@ -2631,17 +2436,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hitachi Announces ‘Metaverse’ Platform That Can Improve Nuclear Plant Construction And Maintenance</t>
+          <t>Iran did not remove 60% enriched uranium from struck nuclear sites - Reuters</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>Fordow</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -2655,7 +2460,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2665,12 +2470,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/hitachi-announces-metaverse-platform-that-can-improve-nuclear-plant-construction-and-maintenance-7-4-2025</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>(35.3802138, 139.1936185)</t>
+          <t>https://www.iranintl.com/en/202507105041</t>
         </is>
       </c>
     </row>
@@ -2682,26 +2482,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>مصادر دفاعية وأمنية تكشف عن تلقي الحوثيين شحنات مواد مشعة وكيماوية تستخدم لتقنية الصواريخ</t>
+          <t>Abu Dhabi Hazardous Materials Management Centre launches 2025-27 strategy</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sa'dah</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45847</v>
+        <v>45854</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2711,29 +2511,24 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.defenseliney.net/posts/295</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>(17.063405, 43.914884)</t>
+          <t>https://www.zawya.com/en/world/middle-east/abu-dhabi-hazardous-materials-management-centre-launches-2025-27-strategy-ksh5nr3b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2743,21 +2538,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>مصادر دفاعية وأمنية تكشف عن تلقي الحوثيين شحنات مواد مشعة وكيماوية تستخدم لتقنية الصواريخ</t>
+          <t>4 هجمات بطائرات مسيّرة خلال 24 ساعة تستهدف حقول نفطية في أربيل ودهوك</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sa'dah</t>
+          <t>Erbil</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45847</v>
+        <v>45854</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2767,111 +2562,105 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.defenseliney.net/posts/295</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>(17.063405, 43.914884)</t>
+          <t>https://baghdadtoday.news/278768-4-24.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gas explosion at residential tower in Tehran injures four: Iranian state media</t>
+          <t>صفعة بحرية للحوثيين بعد ضبط أكبر شحنة أسلحة إيرانية</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Sanaa</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45848</v>
+        <v>45855</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/middle-east/2025/07/10/gas-explosion-at-residential-tower-in-tehran-injures-four-iranian-state-media</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+          <t>https://aawsat.com/%D8%A7%D9%84%D8%B9%D8%A7%D9%84%D9%85-%D8%A7%D9%84%D8%B9%D8%B1%D8%A8%D9%8A/5165487-%D8%B5%D9%81%D8%B9%D8%A9-%D8%A8%D8%AD%D8%B1%D9%8A%D8%A9-%D9%84%D9%84%D8%AD%D9%88%D8%AB%D9%8A%D9%8A%D9%86-%D8%A8%D8%B9%D8%AF-%D8%B6%D8%A8%D8%B7-%D8%A3%D9%83%D8%A8%D8%B1-%D8%B4%D8%AD%D9%86%D8%A9-%D8%A3%D8%B3%D9%84%D8%AD%D8%A9-%D8%A5%D9%8A%D8%B1%D8%A7%D9%86%D9%8A%D8%A9</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gas explosion at residential tower in Tehran injures four: Iranian state media</t>
+          <t>Policy considerations for strengthening preparedness and response to arbovirus epidemics and pandemics</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Geneve</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45848</v>
+        <v>45854</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2885,10 +2674,9 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/middle-east/2025/07/10/gas-explosion-at-residential-tower-in-tehran-injures-four-iranian-state-media</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>https://www.who.int/publications/i/item/9789240108325</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2903,21 +2691,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia slams report it backed ‘zero enrichment’ Iran nuclear deal</t>
+          <t>European Commission Approves €202 Million For Key Fusion Research Facility In Spain</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Escúzar</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45851</v>
+        <v>45854</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2927,7 +2715,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2937,19 +2725,14 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/world/2025/07/13/russia-slams-report-it-backed-zero-enrichment-iran-nuclear-deal-</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>(55.625578, 37.6063916)</t>
+          <t>https://www.nucnet.org/news/european-commission-approves-eur202-million-for-key-fusion-research-facility-in-spain-7-3-2025</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2959,21 +2742,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Update 302 – IAEA Director General Statement on Situation in Ukraine</t>
+          <t>Bahrain, US sign agreement on peaceful nuclear energy</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Zaporizhzhya</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45850</v>
+        <v>45855</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2993,19 +2776,14 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/update-302-iaea-director-general-statement-on-situation-in-ukraine</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>(47.8507859, 35.1182867)</t>
+          <t>https://www.zawya.com/en/business/energy/bahrain-us-sign-agreement-on-peaceful-nuclear-energy-wii2o2u1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3015,21 +2793,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Update 303 – IAEA Director General Statement on Situation in Ukraine</t>
+          <t>Belarus disconnects unit at its nuclear power station after warning</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Zaporizhzhya</t>
+          <t>Astravets</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45851</v>
+        <v>45855</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -3049,12 +2827,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/update-303-iaea-director-general-statement-on-situation-in-ukraine</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>(47.8507859, 35.1182867)</t>
+          <t>https://english.alarabiya.net/News/world/2025/07/17/belarus-disconnects-unit-at-its-nuclear-power-station-after-warning</t>
         </is>
       </c>
     </row>
@@ -3071,21 +2844,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Iran may resume US nuclear talks under no new attacks guarantee</t>
+          <t>Microsoft and Idaho National Laboratory use AI to accelerate nuclear licensing</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45850</v>
+        <v>45855</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3095,7 +2868,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3105,10 +2878,9 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.dailysabah.com/world/mid-east/iran-may-resume-us-nuclear-talks-under-no-new-attacks-guarantee</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
+          <t>https://www.energyconnects.com/news/technology/2025/july/microsoft-and-idaho-national-laboratory-use-ai-to-accelerate-nuclear-licensing/</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3123,21 +2895,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Iran says it will work with IAEA but inspections may be risky</t>
+          <t>NEA launches interactive SMR Dashboard</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45850</v>
+        <v>45855</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3147,7 +2919,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3157,10 +2929,9 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/middle-east/fm-araqchi-says-iran-work-with-iaea-inspections-may-be-risky-2025-07-12/</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>https://www.oecd-nea.org/jcms/pl_108128/nea-launches-interactive-smr-dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3175,21 +2946,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Iran did not remove 60% enriched uranium from struck nuclear sites - Reuters</t>
+          <t>Saudi Arabia and IAEA Discuss Nuclear Program Progress and Emergency Preparedness</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fordow</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45848</v>
+        <v>45854</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -3209,19 +2980,14 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.iranintl.com/en/202507105041</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>(34.9460464, 50.7409863)</t>
+          <t>https://www.arabnews.com/node/2608313/amp</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3231,17 +2997,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Abu Dhabi Hazardous Materials Management Centre launches 2025-27 strategy</t>
+          <t>Raw Materials for Potential Chemical Warfare Agents: Technical Assessment 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
@@ -3255,49 +3021,44 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.zawya.com/en/world/middle-east/abu-dhabi-hazardous-materials-management-centre-launches-2025-27-strategy-ksh5nr3b</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>(24.4538352, 54.3774014)</t>
+          <t>https://www.rusi.org/explore-our-research/publications/special-resources/raw-materials-potential-chemical-warfare-agents-technical-assessment-1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>4 هجمات بطائرات مسيّرة خلال 24 ساعة تستهدف حقول نفطية في أربيل ودهوك</t>
+          <t>Preparing the U.S. Coast Guard for Biological Threats at Sea and Shore</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Erbil</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -3311,7 +3072,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human, Environment</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3321,12 +3082,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://baghdadtoday.news/278768-4-24.html</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>(36.1911744, 44.0094145)</t>
+          <t>https://globalbiodefense.com/2025/07/16/coast-guard-dhs-bioagent-decontamination-ancor/</t>
         </is>
       </c>
     </row>
@@ -3338,22 +3094,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>صفعة بحرية للحوثيين بعد ضبط أكبر شحنة أسلحة إيرانية</t>
+          <t>New U.S. assessment finds American strikes destroyed only one of three Iranian nuclear sites</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sanaa</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
@@ -3367,7 +3123,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3377,12 +3133,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://aawsat.com/%D8%A7%D9%84%D8%B9%D8%A7%D9%84%D9%85-%D8%A7%D9%84%D8%B9%D8%B1%D8%A8%D9%8A/5165487-%D8%B5%D9%81%D8%B9%D8%A9-%D8%A8%D8%AD%D8%B1%D9%8A%D8%A9-%D9%84%D9%84%D8%AD%D9%88%D8%AB%D9%8A%D9%8A%D9%86-%D8%A8%D8%B9%D8%AF-%D8%B6%D8%A8%D8%B7-%D8%A3%D9%83%D8%A8%D8%B1-%D8%B4%D8%AD%D9%86%D8%A9-%D8%A3%D8%B3%D9%84%D8%AD%D8%A9-%D8%A5%D9%8A%D8%B1%D8%A7%D9%86%D9%8A%D8%A9</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>(15.35, 44.2)</t>
+          <t>https://www.nbcnews.com/politics/national-security/new-us-assessment-finds-american-strikes-destroyed-only-one-three-iran-rcna218761</t>
         </is>
       </c>
     </row>
@@ -3394,26 +3145,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Policy considerations for strengthening preparedness and response to arbovirus epidemics and pandemics</t>
+          <t>Iran Update, July 19, 2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Geneve</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45854</v>
+        <v>45857</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3423,7 +3174,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3433,12 +3184,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.who.int/publications/i/item/9789240108325</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
+          <t>https://www.understandingwar.org/backgrounder/iran-update-july-19-2025</t>
         </is>
       </c>
     </row>
@@ -3455,21 +3201,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>European Commission Approves €202 Million For Key Fusion Research Facility In Spain</t>
+          <t>Trump threatens to bomb Iran again if it builds new nuclear plants</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Escúzar</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45854</v>
+        <v>45857</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -3479,7 +3225,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3489,12 +3235,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/european-commission-approves-eur202-million-for-key-fusion-research-facility-in-spain-7-3-2025</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>(37.0621708, -3.7611555)</t>
+          <t>https://www.telegraph.co.uk/world-news/2025/07/19/trump-threatens-to-bomb-iran-again-if-it-builds-new-nuclear/</t>
         </is>
       </c>
     </row>
@@ -3511,21 +3252,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bahrain, US sign agreement on peaceful nuclear energy</t>
+          <t xml:space="preserve">Iran’s ambassador to Moscow: Bushehr nuclear power plant with Russia progressing as planned </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Bushehr</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45855</v>
+        <v>45856</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -3545,12 +3286,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.zawya.com/en/business/energy/bahrain-us-sign-agreement-on-peaceful-nuclear-energy-wii2o2u1</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>(26.2235041, 50.5822436)</t>
+          <t>https://ifpnews.com/irans-ambassador-to-moscow-bushehr-nuclear-power-plant-with-russia-progressing-as-planned/</t>
         </is>
       </c>
     </row>
@@ -3562,36 +3298,36 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belarus disconnects unit at its nuclear power station after warning</t>
+          <t>Explosion kills 3 LASD deputies in East LA; Santa Monica investigation possibly tied to blast</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Astravets</t>
+          <t>California</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45855</v>
+        <v>45857</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human, Infrastructure</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3601,43 +3337,38 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/world/2025/07/17/belarus-disconnects-unit-at-its-nuclear-power-station-after-warning</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>(54.6149379, 25.9565998)</t>
+          <t>https://abc7.com/post/3-deputies-killed-explosion-lasd-facility-east-los-angeles-bomb-squad/17180373/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Microsoft and Idaho National Laboratory use AI to accelerate nuclear licensing</t>
+          <t>KHCO3/sepiolite/CO2 gas-solid composite explosion suppressant on hydrogen/air explosion synergistic inhibition characteristics and inhibition mechanism research</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Guangdong</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45855</v>
+        <v>45857</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -3647,7 +3378,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3657,12 +3388,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.energyconnects.com/news/technology/2025/july/microsoft-and-idaho-national-laboratory-use-ai-to-accelerate-nuclear-licensing/</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>(43.4887907, -112.03628)</t>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0360319925035372</t>
         </is>
       </c>
     </row>
@@ -3679,21 +3405,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NEA launches interactive SMR Dashboard</t>
+          <t>Model predicts long-term effects of nuclear waste on underground disposal systems</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45855</v>
+        <v>45856</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -3703,7 +3429,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Technology, Environment</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3713,12 +3439,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.oecd-nea.org/jcms/pl_108128/nea-launches-interactive-smr-dashboard</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>(48.9759637, 2.1998877)</t>
+          <t>https://news.mit.edu/2025/model-predicts-long-term-effects-nuclear-waste-underground-disposal-systems-0718</t>
         </is>
       </c>
     </row>
@@ -3735,21 +3456,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Saudi Arabia and IAEA Discuss Nuclear Program Progress and Emergency Preparedness</t>
+          <t>Türkiye, S. Korea agree to deepen defense, nuclear, green energy co-op</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45854</v>
+        <v>45855</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -3769,43 +3490,38 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.arabnews.com/node/2608313/amp</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>(23.333333, 45.333333)</t>
+          <t>https://www.dailysabah.com/business/economy/turkiye-s-korea-agree-to-deepen-defense-nuclear-green-energy-co-op</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Raw Materials for Potential Chemical Warfare Agents: Technical Assessment 1</t>
+          <t>Scientists develop rapid, cell-free platform for assembling Nipah virus vaccine prototypes</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45854</v>
+        <v>45856</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -3815,796 +3531,19 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.rusi.org/explore-our-research/publications/special-resources/raw-materials-potential-chemical-warfare-agents-technical-assessment-1</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>(51.5029954, -0.0014602)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Preparing the U.S. Coast Guard for Biological Threats at Sea and Shore</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Washington D.C.</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>45854</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>https://globalbiodefense.com/2025/07/16/coast-guard-dhs-bioagent-decontamination-ancor/</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Preparing the U.S. Coast Guard for Biological Threats at Sea and Shore</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Washington D.C.</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>45854</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://globalbiodefense.com/2025/07/16/coast-guard-dhs-bioagent-decontamination-ancor/</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>New U.S. assessment finds American strikes destroyed only one of three Iranian nuclear sites</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Tehran</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>45855</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>https://www.nbcnews.com/politics/national-security/new-us-assessment-finds-american-strikes-destroyed-only-one-three-iran-rcna218761</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Iran Update, July 19, 2025</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Tehran</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>45857</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>https://www.understandingwar.org/backgrounder/iran-update-july-19-2025</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Trump threatens to bomb Iran again if it builds new nuclear plants</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Washington D.C.</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>45857</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>https://www.telegraph.co.uk/world-news/2025/07/19/trump-threatens-to-bomb-iran-again-if-it-builds-new-nuclear/</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Iran’s ambassador to Moscow: Bushehr nuclear power plant with Russia progressing as planned </t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Bushehr</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>45856</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>https://ifpnews.com/irans-ambassador-to-moscow-bushehr-nuclear-power-plant-with-russia-progressing-as-planned/</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>(28.8936645, 51.3204877)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Incident</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Explosive</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Explosion kills 3 LASD deputies in East LA; Santa Monica investigation possibly tied to blast</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>45857</v>
-      </c>
-      <c r="G68" t="n">
-        <v>3</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>https://abc7.com/post/3-deputies-killed-explosion-lasd-facility-east-los-angeles-bomb-squad/17180373/</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>(37.3503003, -121.9467809)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Incident</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Explosive</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Explosion kills 3 LASD deputies in East LA; Santa Monica investigation possibly tied to blast</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>45857</v>
-      </c>
-      <c r="G69" t="n">
-        <v>3</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>https://abc7.com/post/3-deputies-killed-explosion-lasd-facility-east-los-angeles-bomb-squad/17180373/</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>(37.3503003, -121.9467809)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Study</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Explosive</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>KHCO3/sepiolite/CO2 gas-solid composite explosion suppressant on hydrogen/air explosion synergistic inhibition characteristics and inhibition mechanism research</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Guangdong</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>45857</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0360319925035372</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>(23.1357694, 113.1982688)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Model predicts long-term effects of nuclear waste on underground disposal systems</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Massachusetts</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>45856</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>https://news.mit.edu/2025/model-predicts-long-term-effects-nuclear-waste-underground-disposal-systems-0718</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>(42.3788774, -72.032366)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Model predicts long-term effects of nuclear waste on underground disposal systems</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Massachusetts</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>45856</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>https://news.mit.edu/2025/model-predicts-long-term-effects-nuclear-waste-underground-disposal-systems-0718</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>(42.3788774, -72.032366)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Türkiye, S. Korea agree to deepen defense, nuclear, green energy co-op</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Turkey</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Ankara</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>45855</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>https://www.dailysabah.com/business/economy/turkiye-s-korea-agree-to-deepen-defense-nuclear-green-energy-co-op</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>(39.9207759, 32.8540497)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Study</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Scientists develop rapid, cell-free platform for assembling Nipah virus vaccine prototypes</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>45856</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
           <t>https://phys.org/news/2025-07-scientists-rapid-cell-free-platform.html</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>(40.7856117, -74.0093129)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Epidemic and emerging disease alerts in the Pacific as of 8 July 2025</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>45846</v>
-      </c>
-      <c r="G75" t="n">
-        <v>12</v>
-      </c>
-      <c r="H75" t="n">
-        <v>584</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>https://reliefweb.int/map/world/epidemic-and-emerging-disease-alerts-pacific-8-july-2025</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
